--- a/output/pdf_financials_xlsx/ARQ.xlsx
+++ b/output/pdf_financials_xlsx/ARQ.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ARQ.xlsx
+++ b/output/pdf_financials_xlsx/ARQ.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.158559</v>
+        <v>0.175161</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.195164</v>
@@ -583,7 +583,7 @@
         <v>0.600118</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.556081</v>
+        <v>0.556081</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>1.641517</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.075936</v>
+        <v>0.963774</v>
       </c>
     </row>
     <row r="12">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.003633</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.08963400000000001</v>
+        <v>0.389634</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>3e-06</v>
+        <v>0.342627</v>
       </c>
     </row>
     <row r="65">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.317337</v>
+        <v>0.617337</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.289339</v>
+        <v>0.6319630000000001</v>
       </c>
     </row>
     <row r="69">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.423177</v>
+        <v>1.123177</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1.465889</v>
+        <v>1.123265</v>
       </c>
     </row>
     <row r="76">
@@ -2158,10 +2158,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2176,10 +2174,8 @@
       <c r="C101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2194,10 +2190,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2244,10 +2238,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2278,10 +2270,8 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2296,10 +2286,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2314,10 +2302,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2332,10 +2318,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2350,10 +2334,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2368,10 +2350,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2386,10 +2366,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2404,10 +2382,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2422,10 +2398,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2440,10 +2414,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2458,10 +2430,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2476,10 +2446,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2512,10 +2480,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2530,10 +2496,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2548,10 +2512,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2566,10 +2528,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2584,10 +2544,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2602,10 +2560,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2620,10 +2576,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2660,10 +2614,8 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2712,10 +2664,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2730,10 +2680,8 @@
       <c r="C132" s="3" t="n">
         <v>0.215026</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>-0.159898</v>
       </c>
     </row>
     <row r="133">
@@ -2748,10 +2696,8 @@
       <c r="C133" s="3" t="n">
         <v>0.289915</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.130017</v>
       </c>
     </row>
     <row r="134">
@@ -2766,10 +2712,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2801,7 +2745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2860,7 +2804,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash $ 130,017 $</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2874,10 +2818,10 @@
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.08991499999999999</v>
+        <v>0.289915</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.130017</v>
       </c>
     </row>
     <row r="3">
@@ -3145,7 +3089,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accounts payable $ 342,627 $</t>
+          <t>Accounts payable $</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3159,10 +3103,10 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.08963400000000001</v>
+        <v>0.389634</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.342627</v>
       </c>
     </row>
     <row r="12">
@@ -3487,7 +3431,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Subsequent event Note 14</t>
+          <t>Subsequent event                         Note 14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3926,7 +3870,11 @@
           <t>Equipment 8 1,075</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4800,7 +4748,11 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5058,20 +5010,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cash, end of year $130,017</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0.074889</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.08991499999999999</v>
+        <v>0.289915</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.130017</v>
       </c>
     </row>
     <row r="73">
@@ -5435,24 +5389,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>(c)  Approval of the Financial Statements</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>(c)  Approval of the Financial Statements total</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>0.074889</v>
+        <v>0.002025</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.289915</v>
+        <v>2.9e-05</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5463,30 +5413,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>(c)</t>
-        </is>
-      </c>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>(c) total</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Revenue 12 $</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
-        <v>0.002025</v>
+        <v>0.952692</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>2.9e-05</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.241635</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>1.519855</v>
       </c>
     </row>
     <row r="86">
@@ -5495,25 +5443,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Revenue 12 $</t>
+          <t>Oil and gas operating expenses 7</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>0.952692</v>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>2.241635</v>
+        <v>0.59538</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1.519855</v>
+        <v>0.493071</v>
       </c>
     </row>
     <row r="87">
@@ -5529,24 +5483,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oil and gas operating expenses 7</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Oil and gas depletion, depreciation and accretion 7,13</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.59538</v>
+        <v>0.399828</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.493071</v>
+        <v>0.419039</v>
       </c>
     </row>
     <row r="88">
@@ -5562,20 +5512,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oil and gas depletion, depreciation and accretion 7,13</t>
+          <t>Mineral properties exploration and evaluation 6</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>0.07177500000000001</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.399828</v>
+        <v>0.025937</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.419039</v>
+        <v>0.040439</v>
       </c>
     </row>
     <row r="89">
@@ -5591,18 +5539,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mineral properties exploration and evaluation 6</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Management fees 10</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
-        <v>0.07177500000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.025937</v>
+        <v>0.06</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.040439</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="90">
@@ -5618,7 +5570,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5627,13 +5579,13 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.06</v>
+        <v>0.008300999999999999</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.06</v>
+        <v>0.010636</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.12</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="91">
@@ -5649,22 +5601,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>-0.008300999999999999</v>
+        <v>0.156064</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.010636</v>
+        <v>0.22844</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0494</v>
+        <v>0.222943</v>
       </c>
     </row>
     <row r="92">
@@ -5680,22 +5632,18 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Business development</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
-        <v>0.156064</v>
+        <v>0.044074</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.22844</v>
+        <v>0.131393</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.222943</v>
+        <v>0.045206</v>
       </c>
     </row>
     <row r="93">
@@ -5711,18 +5659,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Business development</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
-        <v>0.044074</v>
+        <v>0.058632</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.131393</v>
+        <v>0.09256300000000001</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.045206</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -5738,22 +5690,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.058632</v>
+        <v>0.066251</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.09256300000000001</v>
+        <v>0.062511</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.10117</v>
       </c>
     </row>
     <row r="95">
@@ -5769,22 +5721,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Listing filing and regulatory fees</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0.066251</v>
+        <v>0.048228</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.062511</v>
+        <v>0.031965</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.10117</v>
+        <v>0.029457</v>
       </c>
     </row>
     <row r="96">
@@ -5800,22 +5752,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Listing filing and regulatory fees</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>0.048228</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0.031965</v>
+          <t>Impairment of oil and gas assets 7</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.029457</v>
+        <v>0.481023</v>
       </c>
     </row>
     <row r="97">
@@ -5831,22 +5783,18 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Impairment of oil and gas assets 7</t>
+          <t>Depreciation - office equipment 8</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="5" t="n">
+        <v>0.003947</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.002864</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.481023</v>
+        <v>0.002188</v>
       </c>
     </row>
     <row r="98">
@@ -5862,18 +5810,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Depreciation - office equipment 8</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TotalExpenses</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
-        <v>0.003947</v>
+        <v>0.786425</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.002864</v>
+        <v>1.641517</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.002188</v>
+        <v>2.075936</v>
       </c>
     </row>
     <row r="99">
@@ -5889,22 +5841,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0.786425</v>
+        <v>0.166267</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>1.641517</v>
+        <v>0.600118</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>2.075936</v>
+        <v>0.556081</v>
       </c>
     </row>
     <row r="100">
@@ -5920,22 +5872,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Bank charges and other</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>0.166267</v>
+        <v>-0.001454</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.600118</v>
+        <v>-0.001589</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-0.556081</v>
+        <v>-0.019069</v>
       </c>
     </row>
     <row r="101">
@@ -5951,18 +5899,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bank charges and other</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
-        <v>-0.001454</v>
+        <v>0.001299</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-0.001589</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>-0.019069</v>
+        <v>0.007508</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -5978,24 +5932,18 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
+          <t>Interest expense - short-term loan 10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" s="5" t="n">
-        <v>0.001299</v>
+        <v>-0.137485</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.007508</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.11022</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.135232</v>
       </c>
     </row>
     <row r="103">
@@ -6011,18 +5959,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Interest expense - short-term loan 10</t>
+          <t>Financing fees- short-term loan 10</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" s="5" t="n">
-        <v>-0.137485</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.11022</v>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.135232</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="104">
@@ -6038,7 +5990,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Financing fees- short-term loan 10</t>
+          <t>Realized loss on investment 10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -6053,7 +6005,7 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.010565</v>
       </c>
     </row>
     <row r="105">
@@ -6069,7 +6021,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Realized loss on investment 10</t>
+          <t>Realized loss on notes receivable</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -6078,13 +6030,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>-0.010565</v>
+      <c r="F105" s="5" t="n">
+        <v>-0.058733</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6100,22 +6052,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Realized loss on notes receivable</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-0.280003</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-0.058733</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.437084</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-0.920947</v>
       </c>
     </row>
     <row r="107">
@@ -6131,22 +6083,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net comprehensive income (loss) for the year</t>
+          <t>Basic and fully diluted earnings per share</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>-0.280003</v>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.437084</v>
+        <v>1e-08</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.920947</v>
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="108">
@@ -6162,24 +6116,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Basic and fully diluted earnings per share</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>1e-08</v>
+        <v>73.565524</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-1e-08</v>
+        <v>72.087774</v>
       </c>
     </row>
     <row r="109">
@@ -6195,20 +6145,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Oil and gas operating expenses</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0.17407</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>73.565524</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>72.087774</v>
+        <v>0.59538</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -6224,19 +6178,15 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oil and gas operating expenses</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Oil and gas depletion, depreciation and accretion 7, 13</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" s="5" t="n">
-        <v>0.17407</v>
+        <v>0.111685</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.59538</v>
+        <v>0.399828</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6257,15 +6207,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oil and gas depletion, depreciation and accretion 7, 13</t>
+          <t>Realized loss on sale of investments</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" s="5" t="n">
-        <v>0.111685</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0.399828</v>
+        <v>-0.01863</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6286,12 +6238,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Realized loss on sale of investments</t>
+          <t>Realized loss on impairment of mineral property 6</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" s="5" t="n">
-        <v>-0.01863</v>
+        <v>-0.29</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6317,17 +6269,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Realized loss on impairment of mineral property 6</t>
+          <t>Realized loss on notes receivable 10</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>-0.058733</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6348,17 +6300,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Realized loss on notes receivable 10</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and diluted earnings per share</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.058733</v>
+        <v>1e-08</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6379,50 +6333,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Basic and diluted earnings per share</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>72.335581</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>1e-08</v>
+        <v>73.565524</v>
       </c>
       <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Weighted average number of shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>72.335581</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>73.565524</v>
-      </c>
-      <c r="G116" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/ARQ.xlsx
+++ b/output/pdf_financials_xlsx/ARQ.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.166267</v>
+        <v>0.786425</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.600118</v>
+        <v>1.641517</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.556081</v>
+        <v>2.075936</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.786425</v>
+        <v>0.166267</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.641517</v>
+        <v>0.600118</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.963774</v>
+        <v>-0.556081</v>
       </c>
     </row>
     <row r="12">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001299</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007508</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.280003</v>
+        <v>-0.281302</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.437084</v>
+        <v>0.429576</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.920947</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.280003</v>
+        <v>-0.281302</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.437084</v>
+        <v>0.429576</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.920947</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-29.39071599215696</v>
+        <v>-29.52706646009413</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>19.49844644645538</v>
+        <v>19.16351234701457</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-60.594398807781</v>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.289915</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.130017</v>
       </c>
     </row>
     <row r="35">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.289915</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.130017</v>
       </c>
     </row>
     <row r="37">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.240265</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.134009</v>
+        <v>0.003992</v>
       </c>
     </row>
     <row r="49">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">

--- a/output/pdf_financials_xlsx/ARQ.xlsx
+++ b/output/pdf_financials_xlsx/ARQ.xlsx
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.044388</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5174,7 +5174,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>0.044388</v>
       </c>
